--- a/DEMAND.xlsx
+++ b/DEMAND.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\revan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\revan\Desktop\demand_planning_agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -116,9 +116,6 @@
     <t>MALKIST SUGAR GB 16 X 30 X 18G</t>
   </si>
   <si>
-    <t>SKU10</t>
-  </si>
-  <si>
     <t>MALKIST SUGAR CRACKERS</t>
   </si>
   <si>
@@ -128,96 +125,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>SKU11</t>
-  </si>
-  <si>
-    <t>SKU12</t>
-  </si>
-  <si>
-    <t>SKU13</t>
-  </si>
-  <si>
-    <t>SKU14</t>
-  </si>
-  <si>
-    <t>SKU15</t>
-  </si>
-  <si>
-    <t>SKU16</t>
-  </si>
-  <si>
-    <t>SKU17</t>
-  </si>
-  <si>
-    <t>SKU18</t>
-  </si>
-  <si>
-    <t>SKU19</t>
-  </si>
-  <si>
-    <t>SKU20</t>
-  </si>
-  <si>
-    <t>SKU21</t>
-  </si>
-  <si>
-    <t>SKU22</t>
-  </si>
-  <si>
-    <t>SKU23</t>
-  </si>
-  <si>
-    <t>SKU24</t>
-  </si>
-  <si>
-    <t>SKU25</t>
-  </si>
-  <si>
-    <t>SKU26</t>
-  </si>
-  <si>
-    <t>SKU27</t>
-  </si>
-  <si>
-    <t>SKU28</t>
-  </si>
-  <si>
-    <t>SKU29</t>
-  </si>
-  <si>
-    <t>SKU30</t>
-  </si>
-  <si>
-    <t>SKU31</t>
-  </si>
-  <si>
-    <t>SKU32</t>
-  </si>
-  <si>
-    <t>SKU33</t>
-  </si>
-  <si>
-    <t>SKU34</t>
-  </si>
-  <si>
-    <t>SKU35</t>
-  </si>
-  <si>
-    <t>SKU36</t>
-  </si>
-  <si>
-    <t>SKU37</t>
-  </si>
-  <si>
-    <t>SKU38</t>
-  </si>
-  <si>
-    <t>SKU39</t>
-  </si>
-  <si>
-    <t>SKU40</t>
-  </si>
-  <si>
     <t>MALKIST CHEESE MINI PACK</t>
   </si>
   <si>
@@ -396,6 +303,99 @@
   </si>
   <si>
     <t>MALKIST SUGAR SHIPPER 100 PCS X 80GM - BULK TRADE CASE</t>
+  </si>
+  <si>
+    <t>SKU011</t>
+  </si>
+  <si>
+    <t>SKU012</t>
+  </si>
+  <si>
+    <t>SKU013</t>
+  </si>
+  <si>
+    <t>SKU014</t>
+  </si>
+  <si>
+    <t>SKU015</t>
+  </si>
+  <si>
+    <t>SKU016</t>
+  </si>
+  <si>
+    <t>SKU017</t>
+  </si>
+  <si>
+    <t>SKU018</t>
+  </si>
+  <si>
+    <t>SKU019</t>
+  </si>
+  <si>
+    <t>SKU020</t>
+  </si>
+  <si>
+    <t>SKU021</t>
+  </si>
+  <si>
+    <t>SKU022</t>
+  </si>
+  <si>
+    <t>SKU023</t>
+  </si>
+  <si>
+    <t>SKU024</t>
+  </si>
+  <si>
+    <t>SKU025</t>
+  </si>
+  <si>
+    <t>SKU026</t>
+  </si>
+  <si>
+    <t>SKU027</t>
+  </si>
+  <si>
+    <t>SKU028</t>
+  </si>
+  <si>
+    <t>SKU029</t>
+  </si>
+  <si>
+    <t>SKU030</t>
+  </si>
+  <si>
+    <t>SKU031</t>
+  </si>
+  <si>
+    <t>SKU032</t>
+  </si>
+  <si>
+    <t>SKU033</t>
+  </si>
+  <si>
+    <t>SKU034</t>
+  </si>
+  <si>
+    <t>SKU035</t>
+  </si>
+  <si>
+    <t>SKU036</t>
+  </si>
+  <si>
+    <t>SKU037</t>
+  </si>
+  <si>
+    <t>SKU038</t>
+  </si>
+  <si>
+    <t>SKU039</t>
+  </si>
+  <si>
+    <t>SKU040</t>
+  </si>
+  <si>
+    <t>SKU010</t>
   </si>
 </sst>
 </file>
@@ -785,7 +785,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -889,343 +889,343 @@
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/DEMAND.xlsx
+++ b/DEMAND.xlsx
@@ -305,104 +305,104 @@
     <t>MALKIST SUGAR SHIPPER 100 PCS X 80GM - BULK TRADE CASE</t>
   </si>
   <si>
-    <t>SKU011</t>
-  </si>
-  <si>
-    <t>SKU012</t>
-  </si>
-  <si>
-    <t>SKU013</t>
-  </si>
-  <si>
-    <t>SKU014</t>
-  </si>
-  <si>
-    <t>SKU015</t>
-  </si>
-  <si>
-    <t>SKU016</t>
-  </si>
-  <si>
-    <t>SKU017</t>
-  </si>
-  <si>
-    <t>SKU018</t>
-  </si>
-  <si>
-    <t>SKU019</t>
-  </si>
-  <si>
-    <t>SKU020</t>
-  </si>
-  <si>
-    <t>SKU021</t>
-  </si>
-  <si>
-    <t>SKU022</t>
-  </si>
-  <si>
-    <t>SKU023</t>
-  </si>
-  <si>
-    <t>SKU024</t>
-  </si>
-  <si>
-    <t>SKU025</t>
-  </si>
-  <si>
-    <t>SKU026</t>
-  </si>
-  <si>
-    <t>SKU027</t>
-  </si>
-  <si>
-    <t>SKU028</t>
-  </si>
-  <si>
-    <t>SKU029</t>
-  </si>
-  <si>
-    <t>SKU030</t>
-  </si>
-  <si>
-    <t>SKU031</t>
-  </si>
-  <si>
-    <t>SKU032</t>
-  </si>
-  <si>
-    <t>SKU033</t>
-  </si>
-  <si>
-    <t>SKU034</t>
-  </si>
-  <si>
-    <t>SKU035</t>
-  </si>
-  <si>
-    <t>SKU036</t>
-  </si>
-  <si>
-    <t>SKU037</t>
-  </si>
-  <si>
-    <t>SKU038</t>
-  </si>
-  <si>
-    <t>SKU039</t>
-  </si>
-  <si>
-    <t>SKU040</t>
-  </si>
-  <si>
-    <t>SKU010</t>
+    <t>SKU10</t>
+  </si>
+  <si>
+    <t>SKU11</t>
+  </si>
+  <si>
+    <t>SKU12</t>
+  </si>
+  <si>
+    <t>SKU13</t>
+  </si>
+  <si>
+    <t>SKU14</t>
+  </si>
+  <si>
+    <t>SKU15</t>
+  </si>
+  <si>
+    <t>SKU16</t>
+  </si>
+  <si>
+    <t>SKU17</t>
+  </si>
+  <si>
+    <t>SKU18</t>
+  </si>
+  <si>
+    <t>SKU19</t>
+  </si>
+  <si>
+    <t>SKU20</t>
+  </si>
+  <si>
+    <t>SKU21</t>
+  </si>
+  <si>
+    <t>SKU22</t>
+  </si>
+  <si>
+    <t>SKU23</t>
+  </si>
+  <si>
+    <t>SKU24</t>
+  </si>
+  <si>
+    <t>SKU25</t>
+  </si>
+  <si>
+    <t>SKU26</t>
+  </si>
+  <si>
+    <t>SKU27</t>
+  </si>
+  <si>
+    <t>SKU28</t>
+  </si>
+  <si>
+    <t>SKU29</t>
+  </si>
+  <si>
+    <t>SKU30</t>
+  </si>
+  <si>
+    <t>SKU31</t>
+  </si>
+  <si>
+    <t>SKU32</t>
+  </si>
+  <si>
+    <t>SKU33</t>
+  </si>
+  <si>
+    <t>SKU34</t>
+  </si>
+  <si>
+    <t>SKU35</t>
+  </si>
+  <si>
+    <t>SKU36</t>
+  </si>
+  <si>
+    <t>SKU37</t>
+  </si>
+  <si>
+    <t>SKU38</t>
+  </si>
+  <si>
+    <t>SKU39</t>
+  </si>
+  <si>
+    <t>SKU40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,6 +421,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF212121"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -472,9 +478,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -484,6 +487,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -769,8 +775,8 @@
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="34.109375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="69.6640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="34.109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="69.6640625" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -778,10 +784,10 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -792,10 +798,10 @@
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -803,10 +809,10 @@
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -814,10 +820,10 @@
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -825,10 +831,10 @@
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -836,10 +842,10 @@
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -847,10 +853,10 @@
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -858,10 +864,10 @@
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -869,10 +875,10 @@
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -880,351 +886,351 @@
       <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>92</v>
       </c>
     </row>
